--- a/templates/_masters/TAX-010-cost-segregation-diy-BLANK.xlsx
+++ b/templates/_masters/TAX-010-cost-segregation-diy-BLANK.xlsx
@@ -38,7 +38,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,12 @@
       <i val="1"/>
       <color rgb="00C9A24B"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="00C9A24B"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Consolas"/>
@@ -306,7 +312,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE7E7"/>
+        <fgColor rgb="00FFCCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -491,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -506,273 +512,279 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="22" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="27" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="33" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="35" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="36" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1211,22 +1223,14 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n"/>
-      <c r="H6" s="1" t="n"/>
-      <c r="I6" s="1" t="n"/>
-      <c r="J6" s="1" t="n"/>
-      <c r="K6" s="1" t="n"/>
-      <c r="L6" s="1" t="n"/>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5">
+        <f>IF(IFERROR('Y1 Summary'!F12,0)&gt;0,"✅  Year-1 deduction = "&amp;TEXT('Y1 Summary'!F12,"$#,##0")&amp;"  ·  Tax savings = "&amp;TEXT('Y1 Summary'!F20,"$#,##0"),"📊  Fill Property Basics + Land Allocation to see your acceleration.")</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>TAX-010 · v2.3 · BLANK</t>
         </is>
@@ -1247,69 +1251,69 @@
       <c r="L8" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>What you'll get</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>⚡ MUCH BIGGER YEAR 1</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>🛡 AUDIT-DEFENSIBLE</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>📄 CPA HAND-OFF</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Reclassify 5/7/15-year components out of the default 27.5-year schedule. Overlay bonus depreciation. Typical STR pulls $30K–$60K extra into Year 1.</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Methodology disclosure block, supporting-document checklist, and per-class sanity guardrails — built per the IRS Cost Segregation Audit Techniques Guide.</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Print-ready Form 4562 mirror (Parts I / II / III) plus the per-asset breakdown your CPA needs — including for a Form 3115 retroactive catch-up.</t>
         </is>
@@ -1321,299 +1325,299 @@
     <row r="18" ht="22" customHeight="1"/>
     <row r="19" ht="22" customHeight="1"/>
     <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="10" t="n"/>
-      <c r="L22" s="10" t="n"/>
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="11" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Quick Start — be done in 90 minutes</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>① Property Basics: purchase + closing + placed-in-service</t>
         </is>
       </c>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>④ Itemize 7-year (furniture, electronics, kitchen)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>② Land Allocation: county-assessor ratio method</t>
         </is>
       </c>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>⑤ Itemize 15-year exterior (drive, landscape, fence, deck)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>③ Itemize 5-year property (carpet, appliances, hot tub…)</t>
         </is>
       </c>
-      <c r="G26" s="10" t="n"/>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t>⑥ Print Form 4562 mirror — hand to CPA</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="10" t="n"/>
-      <c r="J27" s="10" t="n"/>
-      <c r="K27" s="10" t="n"/>
-      <c r="L27" s="10" t="n"/>
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="11" t="n"/>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="10" t="n"/>
-      <c r="K28" s="10" t="n"/>
-      <c r="L28" s="10" t="n"/>
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="11" t="n"/>
+      <c r="K28" s="11" t="n"/>
+      <c r="L28" s="11" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="10" t="n"/>
-      <c r="K29" s="10" t="n"/>
-      <c r="L29" s="10" t="n"/>
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="11" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="13">
+      <c r="A31" s="14">
         <f>HYPERLINK("#'Property Basics'!A5", "GET STARTED — PROPERTY BASICS  →")</f>
         <v/>
       </c>
-      <c r="B31" s="14" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="14" t="n"/>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="14" t="n"/>
-      <c r="I31" s="14" t="n"/>
-      <c r="J31" s="14" t="n"/>
-      <c r="K31" s="14" t="n"/>
-      <c r="L31" s="14" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="15" t="n"/>
+      <c r="K31" s="15" t="n"/>
+      <c r="L31" s="15" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="14" t="n"/>
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="14" t="n"/>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="14" t="n"/>
-      <c r="K32" s="14" t="n"/>
-      <c r="L32" s="14" t="n"/>
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="15" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="14" t="n"/>
-      <c r="B33" s="14" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="14" t="n"/>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="14" t="n"/>
-      <c r="I33" s="14" t="n"/>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="14" t="n"/>
-      <c r="L33" s="14" t="n"/>
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="15" t="n"/>
+      <c r="K33" s="15" t="n"/>
+      <c r="L33" s="15" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="14" t="n"/>
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="14" t="n"/>
-      <c r="H34" s="14" t="n"/>
-      <c r="I34" s="14" t="n"/>
-      <c r="J34" s="14" t="n"/>
-      <c r="K34" s="14" t="n"/>
-      <c r="L34" s="14" t="n"/>
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
+      <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="15" t="n"/>
+      <c r="L34" s="15" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Progress:</t>
         </is>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="17">
         <f>TEXT(MIN((COUNTA('Property Basics'!B8:B9,'Property Basics'!B11:B13) + COUNTA('Land Allocation'!B8:B9) + COUNTA('5-Year Property'!C8:C19) + COUNTA('7-Year Property'!C8:C17) + COUNTA('15-Year Property'!C8:C17))/39,1),"0%") &amp; " complete"</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>① Property Basics</t>
         </is>
       </c>
-      <c r="G39" s="18">
+      <c r="G39" s="19">
         <f>IF(COUNTA('Property Basics'!B8:B9,'Property Basics'!B11:B13)=0,"⏳ Empty","⏳ "&amp;COUNTA('Property Basics'!B8:B9,'Property Basics'!B11:B13)&amp;" of up to 5")</f>
         <v/>
       </c>
-      <c r="K39" s="19">
+      <c r="K39" s="20">
         <f>HYPERLINK("#'Property Basics'!A5","→ go")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>② Land Allocation</t>
         </is>
       </c>
-      <c r="G40" s="18">
+      <c r="G40" s="19">
         <f>IF(COUNTA('Land Allocation'!B8:B9)=0,"⏳ Empty","⏳ "&amp;COUNTA('Land Allocation'!B8:B9)&amp;" of up to 2")</f>
         <v/>
       </c>
-      <c r="K40" s="19">
+      <c r="K40" s="20">
         <f>HYPERLINK("#'Land Allocation'!A5","→ go")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>③ 5-Year Property</t>
         </is>
       </c>
-      <c r="G41" s="18">
+      <c r="G41" s="19">
         <f>IF(COUNTA('5-Year Property'!C8:C19)=0,"⏳ Empty","⏳ "&amp;COUNTA('5-Year Property'!C8:C19)&amp;" of up to 12")</f>
         <v/>
       </c>
-      <c r="K41" s="19">
+      <c r="K41" s="20">
         <f>HYPERLINK("#'5-Year Property'!A5","→ go")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>④ 7-Year Property</t>
         </is>
       </c>
-      <c r="G42" s="18">
+      <c r="G42" s="19">
         <f>IF(COUNTA('7-Year Property'!C8:C17)=0,"○ Skipped (optional)","⏳ "&amp;COUNTA('7-Year Property'!C8:C17)&amp;" item(s) entered")</f>
         <v/>
       </c>
-      <c r="K42" s="19">
+      <c r="K42" s="20">
         <f>HYPERLINK("#'7-Year Property'!A5","→ go")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>⑤ 15-Year Property</t>
         </is>
       </c>
-      <c r="G43" s="18">
+      <c r="G43" s="19">
         <f>IF(COUNTA('15-Year Property'!C8:C17)=0,"⏳ Empty","⏳ "&amp;COUNTA('15-Year Property'!C8:C17)&amp;" of up to 10")</f>
         <v/>
       </c>
-      <c r="K43" s="19">
+      <c r="K43" s="20">
         <f>HYPERLINK("#'15-Year Property'!A5","→ go")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="n"/>
-      <c r="B46" s="20" t="n"/>
-      <c r="C46" s="20" t="n"/>
-      <c r="D46" s="20" t="n"/>
-      <c r="E46" s="20" t="n"/>
-      <c r="F46" s="20" t="n"/>
-      <c r="G46" s="20" t="n"/>
-      <c r="H46" s="20" t="n"/>
-      <c r="I46" s="20" t="n"/>
-      <c r="J46" s="20" t="n"/>
-      <c r="K46" s="20" t="n"/>
-      <c r="L46" s="20" t="n"/>
+      <c r="A46" s="21" t="n"/>
+      <c r="B46" s="21" t="n"/>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="21" t="n"/>
+      <c r="I46" s="21" t="n"/>
+      <c r="J46" s="21" t="n"/>
+      <c r="K46" s="21" t="n"/>
+      <c r="L46" s="21" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="22" t="inlineStr">
         <is>
           <t>Questions? hello@thestrledger.com</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="A48" s="23" t="inlineStr">
         <is>
           <t>TAX-010 · v2.3 · Free updates forever</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="39">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="H26:L26"/>
     <mergeCell ref="A7:L7"/>
@@ -1651,6 +1655,7 @@
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="A11:L11"/>
     <mergeCell ref="H24:L24"/>
+    <mergeCell ref="A6:L6"/>
     <mergeCell ref="B26:F26"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1697,13 +1702,13 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Launch'!A1", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="59" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="60" t="inlineStr">
         <is>
           <t>SETTINGS</t>
         </is>
@@ -1724,231 +1729,238 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr">
         <is>
           <t>Active tax year · bonus depreciation % · marginal rate · MACRS Y1 % per class.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="102" t="inlineStr">
+      <c r="A5" s="103" t="inlineStr">
         <is>
           <t>Active tax year:</t>
         </is>
       </c>
-      <c r="B5" s="103" t="n">
+      <c r="B5" s="104" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="102" t="inlineStr">
+      <c r="A6" s="103" t="inlineStr">
         <is>
           <t>Bonus depreciation % (placed in service Y1):</t>
         </is>
       </c>
-      <c r="B6" s="104" t="n">
+      <c r="B6" s="105" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="102" t="inlineStr">
+      <c r="A7" s="103" t="inlineStr">
         <is>
           <t>Marginal tax rate (for Y1 savings calc):</t>
         </is>
       </c>
-      <c r="B7" s="104" t="n">
+      <c r="B7" s="105" t="n">
         <v>0.24</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="102" t="inlineStr">
+      <c r="A8" s="103" t="inlineStr">
         <is>
           <t>MACRS Y1 % — 5-year property:</t>
         </is>
       </c>
-      <c r="B8" s="105" t="n">
+      <c r="B8" s="106" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="102" t="inlineStr">
+      <c r="A9" s="103" t="inlineStr">
         <is>
           <t>MACRS Y1 % — 7-year property:</t>
         </is>
       </c>
-      <c r="B9" s="105" t="n">
+      <c r="B9" s="106" t="n">
         <v>0.1429</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="102" t="inlineStr">
+      <c r="A10" s="103" t="inlineStr">
         <is>
           <t>MACRS Y1 % — 15-year property:</t>
         </is>
       </c>
-      <c r="B10" s="105" t="n">
+      <c r="B10" s="106" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="12" ht="8" customHeight="1"/>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="107" t="inlineStr">
+        <is>
+          <t>📅 Bonus % + MACRS Y1 percentages as of 2026-01-01 — bonus phases to 0% by 2028 (statutory). Confirm against IRS Pub 946 yearly.</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="106" t="inlineStr">
+      <c r="A13" s="108" t="inlineStr">
         <is>
           <t>Historical bonus depreciation %:</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="107" t="inlineStr">
+      <c r="A14" s="109" t="inlineStr">
         <is>
           <t>2022:</t>
         </is>
       </c>
-      <c r="B14" s="108" t="n">
+      <c r="B14" s="110" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="107" t="inlineStr">
+      <c r="A15" s="109" t="inlineStr">
         <is>
           <t>2023:</t>
         </is>
       </c>
-      <c r="B15" s="108" t="n">
+      <c r="B15" s="110" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="107" t="inlineStr">
+      <c r="A16" s="109" t="inlineStr">
         <is>
           <t>2024:</t>
         </is>
       </c>
-      <c r="B16" s="108" t="n">
+      <c r="B16" s="110" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="107" t="inlineStr">
+      <c r="A17" s="109" t="inlineStr">
         <is>
           <t>2025:</t>
         </is>
       </c>
-      <c r="B17" s="108" t="n">
+      <c r="B17" s="110" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="107" t="inlineStr">
+      <c r="A18" s="109" t="inlineStr">
         <is>
           <t>2026:</t>
         </is>
       </c>
-      <c r="B18" s="108" t="n">
+      <c r="B18" s="110" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="107" t="inlineStr">
+      <c r="A19" s="109" t="inlineStr">
         <is>
           <t>2027:</t>
         </is>
       </c>
-      <c r="B19" s="108" t="n">
+      <c r="B19" s="110" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="107" t="inlineStr">
+      <c r="A20" s="109" t="inlineStr">
         <is>
           <t>2028:</t>
         </is>
       </c>
-      <c r="B20" s="108" t="n">
+      <c r="B20" s="110" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="8" customHeight="1"/>
     <row r="23">
-      <c r="A23" s="109" t="inlineStr">
+      <c r="A23" s="111" t="inlineStr">
         <is>
           <t>MACRS reference (200% DB half-year):</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="107" t="inlineStr">
+      <c r="A24" s="109" t="inlineStr">
         <is>
           <t>5-yr Y1:</t>
         </is>
       </c>
-      <c r="B24" s="110" t="n">
+      <c r="B24" s="112" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="107" t="inlineStr">
+      <c r="A25" s="109" t="inlineStr">
         <is>
           <t>5-yr Y2:</t>
         </is>
       </c>
-      <c r="B25" s="110" t="n">
+      <c r="B25" s="112" t="n">
         <v>0.32</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="107" t="inlineStr">
+      <c r="A26" s="109" t="inlineStr">
         <is>
           <t>5-yr Y3:</t>
         </is>
       </c>
-      <c r="B26" s="110" t="n">
+      <c r="B26" s="112" t="n">
         <v>0.192</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="107" t="inlineStr">
+      <c r="A27" s="109" t="inlineStr">
         <is>
           <t>7-yr Y1:</t>
         </is>
       </c>
-      <c r="B27" s="110" t="n">
+      <c r="B27" s="112" t="n">
         <v>0.1429</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="107" t="inlineStr">
+      <c r="A28" s="109" t="inlineStr">
         <is>
           <t>7-yr Y2:</t>
         </is>
       </c>
-      <c r="B28" s="110" t="n">
+      <c r="B28" s="112" t="n">
         <v>0.2449</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="107" t="inlineStr">
+      <c r="A29" s="109" t="inlineStr">
         <is>
           <t>15-yr Y1:</t>
         </is>
       </c>
-      <c r="B29" s="110" t="n">
+      <c r="B29" s="112" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="107" t="inlineStr">
+      <c r="A30" s="109" t="inlineStr">
         <is>
           <t>15-yr Y2:</t>
         </is>
       </c>
-      <c r="B30" s="110" t="n">
+      <c r="B30" s="112" t="n">
         <v>0.095</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="D2:L2"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
@@ -1995,23 +2007,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Start'!A1", "← START")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>SECTION 1 OF 5</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'Land Allocation'!A5", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -2028,191 +2040,191 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Property Basics</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Purchase price, closing costs, placed-in-service date.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Fill the highlighted fields below.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>PURCHASE + PLACED-IN-SERVICE</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Purchase price ($):</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="32" t="n"/>
-      <c r="J8" s="32" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="33" t="n"/>
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="33" t="n"/>
+      <c r="I8" s="33" t="n"/>
+      <c r="J8" s="33" t="n"/>
+      <c r="K8" s="33" t="n"/>
+      <c r="L8" s="34" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Capitalizable closing/title costs ($):</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="37" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>TOTAL BASIS:</t>
         </is>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="39">
         <f>B8+B9</f>
         <v/>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="36" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="37" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>Property address:</t>
         </is>
       </c>
-      <c r="B11" s="39" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="36" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="37" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Placed-in-service date:</t>
         </is>
       </c>
-      <c r="B12" s="40" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="36" t="n"/>
+      <c r="B12" s="41" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="37" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>Schedule classification:</t>
         </is>
       </c>
-      <c r="B13" s="42" t="n"/>
-      <c r="C13" s="43" t="n"/>
-      <c r="D13" s="43" t="n"/>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="43" t="n"/>
-      <c r="G13" s="43" t="n"/>
-      <c r="H13" s="43" t="n"/>
-      <c r="I13" s="43" t="n"/>
-      <c r="J13" s="43" t="n"/>
-      <c r="K13" s="43" t="n"/>
-      <c r="L13" s="44" t="n"/>
+      <c r="B13" s="43" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="44" t="n"/>
+      <c r="G13" s="44" t="n"/>
+      <c r="H13" s="44" t="n"/>
+      <c r="I13" s="44" t="n"/>
+      <c r="J13" s="44" t="n"/>
+      <c r="K13" s="44" t="n"/>
+      <c r="L13" s="45" t="n"/>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="45" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>ⓘ Capitalizable closing costs include title insurance, recording fees, transfer taxes, attorney fees, and survey costs — NOT prepaid insurance, prepaid property tax, or financing points (those are deducted differently). Your settlement statement (HUD-1 / Closing Disclosure) lists each line item — when in doubt, ask your CPA which lines are capitalizable.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="45" t="inlineStr">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>ⓘ Placed-in-service date drives the 27.5-year mid-month convention for the building residual. Most STRs are placed in service the day they're first marketed for rental (listing live + photos), not the closing date. Document this with your first listing screenshot.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="46">
+      <c r="A19" s="47">
         <f>HYPERLINK("#'Start'!A1", "← Back: Start")</f>
         <v/>
       </c>
-      <c r="B19" s="47" t="n"/>
-      <c r="C19" s="47" t="n"/>
-      <c r="D19" s="47" t="n"/>
-      <c r="E19" s="47" t="n"/>
-      <c r="F19" s="47" t="n"/>
-      <c r="G19" s="46">
+      <c r="B19" s="48" t="n"/>
+      <c r="C19" s="48" t="n"/>
+      <c r="D19" s="48" t="n"/>
+      <c r="E19" s="48" t="n"/>
+      <c r="F19" s="48" t="n"/>
+      <c r="G19" s="47">
         <f>HYPERLINK("#'Land Allocation'!A5", "Next: Land Allocation →")</f>
         <v/>
       </c>
-      <c r="H19" s="47" t="n"/>
-      <c r="I19" s="47" t="n"/>
-      <c r="J19" s="47" t="n"/>
-      <c r="K19" s="47" t="n"/>
-      <c r="L19" s="47" t="n"/>
+      <c r="H19" s="48" t="n"/>
+      <c r="I19" s="48" t="n"/>
+      <c r="J19" s="48" t="n"/>
+      <c r="K19" s="48" t="n"/>
+      <c r="L19" s="48" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="47" t="n"/>
-      <c r="B20" s="47" t="n"/>
-      <c r="C20" s="47" t="n"/>
-      <c r="D20" s="47" t="n"/>
-      <c r="E20" s="47" t="n"/>
-      <c r="F20" s="47" t="n"/>
-      <c r="G20" s="47" t="n"/>
-      <c r="H20" s="47" t="n"/>
-      <c r="I20" s="47" t="n"/>
-      <c r="J20" s="47" t="n"/>
-      <c r="K20" s="47" t="n"/>
-      <c r="L20" s="47" t="n"/>
+      <c r="A20" s="48" t="n"/>
+      <c r="B20" s="48" t="n"/>
+      <c r="C20" s="48" t="n"/>
+      <c r="D20" s="48" t="n"/>
+      <c r="E20" s="48" t="n"/>
+      <c r="F20" s="48" t="n"/>
+      <c r="G20" s="48" t="n"/>
+      <c r="H20" s="48" t="n"/>
+      <c r="I20" s="48" t="n"/>
+      <c r="J20" s="48" t="n"/>
+      <c r="K20" s="48" t="n"/>
+      <c r="L20" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2276,23 +2288,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Property Basics'!A5", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>SECTION 2 OF 5</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'5-Year Property'!A5", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -2309,206 +2321,206 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Land Allocation</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>County tax assessor ratio method — separates land from depreciable basis.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Look up your county tax assessor's land + improvements values for the property — usually free online.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>COUNTY TAX ASSESSOR RATIO</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>County tax assessor — LAND value ($):</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="32" t="n"/>
-      <c r="J8" s="32" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="33" t="n"/>
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="33" t="n"/>
+      <c r="I8" s="33" t="n"/>
+      <c r="J8" s="33" t="n"/>
+      <c r="K8" s="33" t="n"/>
+      <c r="L8" s="34" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>County tax assessor — IMPROVEMENTS value ($):</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="37" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>County total (land + improvements):</t>
         </is>
       </c>
-      <c r="B10" s="48">
+      <c r="B10" s="49">
         <f>B8+B9</f>
         <v/>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="36" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="37" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>Land ratio (land ÷ county total):</t>
         </is>
       </c>
-      <c r="B11" s="49">
+      <c r="B11" s="50">
         <f>IFERROR(B8/B10,0)</f>
         <v/>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="36" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="37" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>ALLOCATED LAND ($) — non-depreciable:</t>
         </is>
       </c>
-      <c r="B12" s="50">
+      <c r="B12" s="51">
         <f>'Property Basics'!B10*B11</f>
         <v/>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="36" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="37" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>DEPRECIABLE IMPROVEMENTS BASIS:</t>
         </is>
       </c>
-      <c r="B13" s="52">
+      <c r="B13" s="53">
         <f>'Property Basics'!B10-B12</f>
         <v/>
       </c>
-      <c r="C13" s="43" t="n"/>
-      <c r="D13" s="43" t="n"/>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="43" t="n"/>
-      <c r="G13" s="43" t="n"/>
-      <c r="H13" s="43" t="n"/>
-      <c r="I13" s="43" t="n"/>
-      <c r="J13" s="43" t="n"/>
-      <c r="K13" s="43" t="n"/>
-      <c r="L13" s="44" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="44" t="n"/>
+      <c r="G13" s="44" t="n"/>
+      <c r="H13" s="44" t="n"/>
+      <c r="I13" s="44" t="n"/>
+      <c r="J13" s="44" t="n"/>
+      <c r="K13" s="44" t="n"/>
+      <c r="L13" s="45" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="53">
+      <c r="A15" s="54">
         <f>IF(B11=0,"",IF(B11&lt;0.1,"⚠ Land ratio under 10% — confirm county assessor values are correct. STR land is rarely below 10%.",IF(B11&gt;0.35,"⚠ Land ratio over 35% — confirm county assessor values. High land ratio reduces depreciable basis significantly.","")))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="45" t="inlineStr">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>ⓘ The county tax assessor ratio method is the default IRS-accepted approach for DIY land allocation. Alternatives: (a) use the appraisal report's land value if your purchase appraisal broke it out, or (b) hire a land appraiser for ~$300 if you believe the county ratio is unreasonable. Document whichever method you use in the Launch tab's methodology block.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>ⓘ Land is NEVER depreciable — this is the single most-audited line in cost segregation. Auditors compare your land allocation to county records. If you allocate less to land than the county does, be prepared to defend why (e.g., appraisal report, comparable sales).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="46">
+      <c r="A21" s="47">
         <f>HYPERLINK("#'Property Basics'!A5", "← Back: Property Basics")</f>
         <v/>
       </c>
-      <c r="B21" s="47" t="n"/>
-      <c r="C21" s="47" t="n"/>
-      <c r="D21" s="47" t="n"/>
-      <c r="E21" s="47" t="n"/>
-      <c r="F21" s="47" t="n"/>
-      <c r="G21" s="46">
+      <c r="B21" s="48" t="n"/>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+      <c r="E21" s="48" t="n"/>
+      <c r="F21" s="48" t="n"/>
+      <c r="G21" s="47">
         <f>HYPERLINK("#'5-Year Property'!A5", "Next: 5-Year Property →")</f>
         <v/>
       </c>
-      <c r="H21" s="47" t="n"/>
-      <c r="I21" s="47" t="n"/>
-      <c r="J21" s="47" t="n"/>
-      <c r="K21" s="47" t="n"/>
-      <c r="L21" s="47" t="n"/>
+      <c r="H21" s="48" t="n"/>
+      <c r="I21" s="48" t="n"/>
+      <c r="J21" s="48" t="n"/>
+      <c r="K21" s="48" t="n"/>
+      <c r="L21" s="48" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="47" t="n"/>
-      <c r="B22" s="47" t="n"/>
-      <c r="C22" s="47" t="n"/>
-      <c r="D22" s="47" t="n"/>
-      <c r="E22" s="47" t="n"/>
-      <c r="F22" s="47" t="n"/>
-      <c r="G22" s="47" t="n"/>
-      <c r="H22" s="47" t="n"/>
-      <c r="I22" s="47" t="n"/>
-      <c r="J22" s="47" t="n"/>
-      <c r="K22" s="47" t="n"/>
-      <c r="L22" s="47" t="n"/>
+      <c r="A22" s="48" t="n"/>
+      <c r="B22" s="48" t="n"/>
+      <c r="C22" s="48" t="n"/>
+      <c r="D22" s="48" t="n"/>
+      <c r="E22" s="48" t="n"/>
+      <c r="F22" s="48" t="n"/>
+      <c r="G22" s="48" t="n"/>
+      <c r="H22" s="48" t="n"/>
+      <c r="I22" s="48" t="n"/>
+      <c r="J22" s="48" t="n"/>
+      <c r="K22" s="48" t="n"/>
+      <c r="L22" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2568,23 +2580,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Land Allocation'!A5", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>SECTION 3 OF 5</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'7-Year Property'!A5", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -2601,38 +2613,38 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>5-Year Property</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Carpet, appliances, decorative lighting, hot tub, smart-home gear, etc.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>5-year MACRS = personal property used in the rental — the highest-value reclassification class for STRs.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="54" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B7" s="54" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>Item description</t>
         </is>
       </c>
-      <c r="C7" s="54" t="inlineStr">
+      <c r="C7" s="55" t="inlineStr">
         <is>
           <t>Amount ($)</t>
         </is>
@@ -2648,147 +2660,147 @@
       <c r="L7" s="1" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="55" t="n">
+      <c r="A8" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="56" t="n"/>
-      <c r="C8" s="57" t="n"/>
+      <c r="B8" s="57" t="n"/>
+      <c r="C8" s="58" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="55" t="n">
+      <c r="A9" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="56" t="n"/>
-      <c r="C9" s="57" t="n"/>
+      <c r="B9" s="57" t="n"/>
+      <c r="C9" s="58" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="55" t="n">
+      <c r="A10" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="56" t="n"/>
-      <c r="C10" s="57" t="n"/>
+      <c r="B10" s="57" t="n"/>
+      <c r="C10" s="58" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="55" t="n">
+      <c r="A11" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="56" t="n"/>
-      <c r="C11" s="57" t="n"/>
+      <c r="B11" s="57" t="n"/>
+      <c r="C11" s="58" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="55" t="n">
+      <c r="A12" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="56" t="n"/>
-      <c r="C12" s="57" t="n"/>
+      <c r="B12" s="57" t="n"/>
+      <c r="C12" s="58" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="55" t="n">
+      <c r="A13" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="56" t="n"/>
-      <c r="C13" s="57" t="n"/>
+      <c r="B13" s="57" t="n"/>
+      <c r="C13" s="58" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="55" t="n">
+      <c r="A14" s="56" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="56" t="n"/>
-      <c r="C14" s="57" t="n"/>
+      <c r="B14" s="57" t="n"/>
+      <c r="C14" s="58" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="55" t="n">
+      <c r="A15" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="56" t="n"/>
-      <c r="C15" s="57" t="n"/>
+      <c r="B15" s="57" t="n"/>
+      <c r="C15" s="58" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="55" t="n">
+      <c r="A16" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="56" t="n"/>
-      <c r="C16" s="57" t="n"/>
+      <c r="B16" s="57" t="n"/>
+      <c r="C16" s="58" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="55" t="n">
+      <c r="A17" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="56" t="n"/>
-      <c r="C17" s="57" t="n"/>
+      <c r="B17" s="57" t="n"/>
+      <c r="C17" s="58" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="55" t="n">
+      <c r="A18" s="56" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="56" t="n"/>
-      <c r="C18" s="57" t="n"/>
+      <c r="B18" s="57" t="n"/>
+      <c r="C18" s="58" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="55" t="n">
+      <c r="A19" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="56" t="n"/>
-      <c r="C19" s="57" t="n"/>
+      <c r="B19" s="57" t="n"/>
+      <c r="C19" s="58" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="B20" s="58" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>TOTAL:</t>
         </is>
       </c>
-      <c r="C20" s="50">
+      <c r="C20" s="51">
         <f>SUM(C8:C19)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="45" t="inlineStr">
+      <c r="A22" s="46" t="inlineStr">
         <is>
           <t>ⓘ Common 5-year items: appliances (fridge, range, dishwasher, W/D), carpet + area rugs, decorative lighting + ceiling fans, window treatments + blinds, hot tubs + saunas, smart locks + cameras, smart TVs, game-room equipment, initial linens + kitchenware. Some 5-year items also qualify for §179 — see TAX-009 Section 179 Planner.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="A24" s="46" t="inlineStr">
         <is>
           <t>ⓘ For each item, keep supporting documents: vendor invoices, purchase agreement furniture inventory, photos with date metadata, or an inspector report itemization. Vague descriptions ('misc furnishings', 'fixtures') are the #1 audit weak point — be specific and itemized.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="46">
+      <c r="A26" s="47">
         <f>HYPERLINK("#'Land Allocation'!A5", "← Back: Land Allocation")</f>
         <v/>
       </c>
-      <c r="B26" s="47" t="n"/>
-      <c r="C26" s="47" t="n"/>
-      <c r="D26" s="47" t="n"/>
-      <c r="E26" s="47" t="n"/>
-      <c r="F26" s="47" t="n"/>
-      <c r="G26" s="46">
+      <c r="B26" s="48" t="n"/>
+      <c r="C26" s="48" t="n"/>
+      <c r="D26" s="48" t="n"/>
+      <c r="E26" s="48" t="n"/>
+      <c r="F26" s="48" t="n"/>
+      <c r="G26" s="47">
         <f>HYPERLINK("#'7-Year Property'!A5", "Next: 7-Year Property →")</f>
         <v/>
       </c>
-      <c r="H26" s="47" t="n"/>
-      <c r="I26" s="47" t="n"/>
-      <c r="J26" s="47" t="n"/>
-      <c r="K26" s="47" t="n"/>
-      <c r="L26" s="47" t="n"/>
+      <c r="H26" s="48" t="n"/>
+      <c r="I26" s="48" t="n"/>
+      <c r="J26" s="48" t="n"/>
+      <c r="K26" s="48" t="n"/>
+      <c r="L26" s="48" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="47" t="n"/>
-      <c r="B27" s="47" t="n"/>
-      <c r="C27" s="47" t="n"/>
-      <c r="D27" s="47" t="n"/>
-      <c r="E27" s="47" t="n"/>
-      <c r="F27" s="47" t="n"/>
-      <c r="G27" s="47" t="n"/>
-      <c r="H27" s="47" t="n"/>
-      <c r="I27" s="47" t="n"/>
-      <c r="J27" s="47" t="n"/>
-      <c r="K27" s="47" t="n"/>
-      <c r="L27" s="47" t="n"/>
+      <c r="A27" s="48" t="n"/>
+      <c r="B27" s="48" t="n"/>
+      <c r="C27" s="48" t="n"/>
+      <c r="D27" s="48" t="n"/>
+      <c r="E27" s="48" t="n"/>
+      <c r="F27" s="48" t="n"/>
+      <c r="G27" s="48" t="n"/>
+      <c r="H27" s="48" t="n"/>
+      <c r="I27" s="48" t="n"/>
+      <c r="J27" s="48" t="n"/>
+      <c r="K27" s="48" t="n"/>
+      <c r="L27" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2846,23 +2858,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'5-Year Property'!A5", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>SECTION 4 OF 5</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'15-Year Property'!A5", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -2879,38 +2891,38 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>7-Year Property</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Furniture, electronics, kitchen equipment with 7-year recovery.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>7-year MACRS = office/business furniture and certain equipment. Optional — can be combined into 5-year if simpler.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="54" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B7" s="54" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>Item description</t>
         </is>
       </c>
-      <c r="C7" s="54" t="inlineStr">
+      <c r="C7" s="55" t="inlineStr">
         <is>
           <t>Amount ($)</t>
         </is>
@@ -2926,133 +2938,133 @@
       <c r="L7" s="1" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="55" t="n">
+      <c r="A8" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="56" t="n"/>
-      <c r="C8" s="57" t="n"/>
+      <c r="B8" s="57" t="n"/>
+      <c r="C8" s="58" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="55" t="n">
+      <c r="A9" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="56" t="n"/>
-      <c r="C9" s="57" t="n"/>
+      <c r="B9" s="57" t="n"/>
+      <c r="C9" s="58" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="55" t="n">
+      <c r="A10" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="56" t="n"/>
-      <c r="C10" s="57" t="n"/>
+      <c r="B10" s="57" t="n"/>
+      <c r="C10" s="58" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="55" t="n">
+      <c r="A11" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="56" t="n"/>
-      <c r="C11" s="57" t="n"/>
+      <c r="B11" s="57" t="n"/>
+      <c r="C11" s="58" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="55" t="n">
+      <c r="A12" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="56" t="n"/>
-      <c r="C12" s="57" t="n"/>
+      <c r="B12" s="57" t="n"/>
+      <c r="C12" s="58" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="55" t="n">
+      <c r="A13" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="56" t="n"/>
-      <c r="C13" s="57" t="n"/>
+      <c r="B13" s="57" t="n"/>
+      <c r="C13" s="58" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="55" t="n">
+      <c r="A14" s="56" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="56" t="n"/>
-      <c r="C14" s="57" t="n"/>
+      <c r="B14" s="57" t="n"/>
+      <c r="C14" s="58" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="55" t="n">
+      <c r="A15" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="56" t="n"/>
-      <c r="C15" s="57" t="n"/>
+      <c r="B15" s="57" t="n"/>
+      <c r="C15" s="58" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="55" t="n">
+      <c r="A16" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="56" t="n"/>
-      <c r="C16" s="57" t="n"/>
+      <c r="B16" s="57" t="n"/>
+      <c r="C16" s="58" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="55" t="n">
+      <c r="A17" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="56" t="n"/>
-      <c r="C17" s="57" t="n"/>
+      <c r="B17" s="57" t="n"/>
+      <c r="C17" s="58" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="B18" s="58" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>TOTAL:</t>
         </is>
       </c>
-      <c r="C18" s="50">
+      <c r="C18" s="51">
         <f>SUM(C8:C17)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>ⓘ Common 7-year items: office furniture (if you have a workspace in the rental), some commercial-grade kitchen equipment, agricultural or specialty equipment. Most STR personal property fits better in 5-year — leave this tab empty if your items are clearly 5-year.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="45" t="inlineStr">
+      <c r="A22" s="46" t="inlineStr">
         <is>
           <t>ⓘ For each item, keep supporting documents: vendor invoices, purchase agreement furniture inventory, photos with date metadata, or an inspector report itemization. Vague descriptions ('misc furnishings', 'fixtures') are the #1 audit weak point — be specific and itemized.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="46">
+      <c r="A24" s="47">
         <f>HYPERLINK("#'5-Year Property'!A5", "← Back: 5-Year Property")</f>
         <v/>
       </c>
-      <c r="B24" s="47" t="n"/>
-      <c r="C24" s="47" t="n"/>
-      <c r="D24" s="47" t="n"/>
-      <c r="E24" s="47" t="n"/>
-      <c r="F24" s="47" t="n"/>
-      <c r="G24" s="46">
+      <c r="B24" s="48" t="n"/>
+      <c r="C24" s="48" t="n"/>
+      <c r="D24" s="48" t="n"/>
+      <c r="E24" s="48" t="n"/>
+      <c r="F24" s="48" t="n"/>
+      <c r="G24" s="47">
         <f>HYPERLINK("#'15-Year Property'!A5", "Next: 15-Year Property →")</f>
         <v/>
       </c>
-      <c r="H24" s="47" t="n"/>
-      <c r="I24" s="47" t="n"/>
-      <c r="J24" s="47" t="n"/>
-      <c r="K24" s="47" t="n"/>
-      <c r="L24" s="47" t="n"/>
+      <c r="H24" s="48" t="n"/>
+      <c r="I24" s="48" t="n"/>
+      <c r="J24" s="48" t="n"/>
+      <c r="K24" s="48" t="n"/>
+      <c r="L24" s="48" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="47" t="n"/>
-      <c r="B25" s="47" t="n"/>
-      <c r="C25" s="47" t="n"/>
-      <c r="D25" s="47" t="n"/>
-      <c r="E25" s="47" t="n"/>
-      <c r="F25" s="47" t="n"/>
-      <c r="G25" s="47" t="n"/>
-      <c r="H25" s="47" t="n"/>
-      <c r="I25" s="47" t="n"/>
-      <c r="J25" s="47" t="n"/>
-      <c r="K25" s="47" t="n"/>
-      <c r="L25" s="47" t="n"/>
+      <c r="A25" s="48" t="n"/>
+      <c r="B25" s="48" t="n"/>
+      <c r="C25" s="48" t="n"/>
+      <c r="D25" s="48" t="n"/>
+      <c r="E25" s="48" t="n"/>
+      <c r="F25" s="48" t="n"/>
+      <c r="G25" s="48" t="n"/>
+      <c r="H25" s="48" t="n"/>
+      <c r="I25" s="48" t="n"/>
+      <c r="J25" s="48" t="n"/>
+      <c r="K25" s="48" t="n"/>
+      <c r="L25" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3110,23 +3122,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'7-Year Property'!A5", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>SECTION 5 OF 5</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'Y1 Summary'!A5", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -3143,38 +3155,38 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>15-Year Property</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Land improvements — driveway, landscaping, fencing, exterior lighting.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>15-year MACRS = land improvements. NOT the land itself — things attached to or done to the land outside the building.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="54" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B7" s="54" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>Item description</t>
         </is>
       </c>
-      <c r="C7" s="54" t="inlineStr">
+      <c r="C7" s="55" t="inlineStr">
         <is>
           <t>Amount ($)</t>
         </is>
@@ -3190,133 +3202,133 @@
       <c r="L7" s="1" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="55" t="n">
+      <c r="A8" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="56" t="n"/>
-      <c r="C8" s="57" t="n"/>
+      <c r="B8" s="57" t="n"/>
+      <c r="C8" s="58" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="55" t="n">
+      <c r="A9" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="56" t="n"/>
-      <c r="C9" s="57" t="n"/>
+      <c r="B9" s="57" t="n"/>
+      <c r="C9" s="58" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="55" t="n">
+      <c r="A10" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="56" t="n"/>
-      <c r="C10" s="57" t="n"/>
+      <c r="B10" s="57" t="n"/>
+      <c r="C10" s="58" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="55" t="n">
+      <c r="A11" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="56" t="n"/>
-      <c r="C11" s="57" t="n"/>
+      <c r="B11" s="57" t="n"/>
+      <c r="C11" s="58" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="55" t="n">
+      <c r="A12" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="56" t="n"/>
-      <c r="C12" s="57" t="n"/>
+      <c r="B12" s="57" t="n"/>
+      <c r="C12" s="58" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="55" t="n">
+      <c r="A13" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="56" t="n"/>
-      <c r="C13" s="57" t="n"/>
+      <c r="B13" s="57" t="n"/>
+      <c r="C13" s="58" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="55" t="n">
+      <c r="A14" s="56" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="56" t="n"/>
-      <c r="C14" s="57" t="n"/>
+      <c r="B14" s="57" t="n"/>
+      <c r="C14" s="58" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="55" t="n">
+      <c r="A15" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="56" t="n"/>
-      <c r="C15" s="57" t="n"/>
+      <c r="B15" s="57" t="n"/>
+      <c r="C15" s="58" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="55" t="n">
+      <c r="A16" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="56" t="n"/>
-      <c r="C16" s="57" t="n"/>
+      <c r="B16" s="57" t="n"/>
+      <c r="C16" s="58" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="55" t="n">
+      <c r="A17" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="56" t="n"/>
-      <c r="C17" s="57" t="n"/>
+      <c r="B17" s="57" t="n"/>
+      <c r="C17" s="58" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="B18" s="58" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>TOTAL:</t>
         </is>
       </c>
-      <c r="C18" s="50">
+      <c r="C18" s="51">
         <f>SUM(C8:C17)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>ⓘ Common 15-year items: driveway + parking pad, landscaping (plantings, retaining walls, mulch), exterior lighting (path, flood, accent), fencing, exterior decks + stairs (if separate from the building), in-ground sprinklers, walkways, exterior signage. Land improvements are eligible for bonus depreciation (40% in 2026).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="45" t="inlineStr">
+      <c r="A22" s="46" t="inlineStr">
         <is>
           <t>ⓘ For each item, keep supporting documents: vendor invoices, purchase agreement furniture inventory, photos with date metadata, or an inspector report itemization. Vague descriptions ('misc furnishings', 'fixtures') are the #1 audit weak point — be specific and itemized.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="46">
+      <c r="A24" s="47">
         <f>HYPERLINK("#'7-Year Property'!A5", "← Back: 7-Year Property")</f>
         <v/>
       </c>
-      <c r="B24" s="47" t="n"/>
-      <c r="C24" s="47" t="n"/>
-      <c r="D24" s="47" t="n"/>
-      <c r="E24" s="47" t="n"/>
-      <c r="F24" s="47" t="n"/>
-      <c r="G24" s="46">
+      <c r="B24" s="48" t="n"/>
+      <c r="C24" s="48" t="n"/>
+      <c r="D24" s="48" t="n"/>
+      <c r="E24" s="48" t="n"/>
+      <c r="F24" s="48" t="n"/>
+      <c r="G24" s="47">
         <f>HYPERLINK("#'Y1 Summary'!A5", "Next: Y1 Summary →")</f>
         <v/>
       </c>
-      <c r="H24" s="47" t="n"/>
-      <c r="I24" s="47" t="n"/>
-      <c r="J24" s="47" t="n"/>
-      <c r="K24" s="47" t="n"/>
-      <c r="L24" s="47" t="n"/>
+      <c r="H24" s="48" t="n"/>
+      <c r="I24" s="48" t="n"/>
+      <c r="J24" s="48" t="n"/>
+      <c r="K24" s="48" t="n"/>
+      <c r="L24" s="48" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="47" t="n"/>
-      <c r="B25" s="47" t="n"/>
-      <c r="C25" s="47" t="n"/>
-      <c r="D25" s="47" t="n"/>
-      <c r="E25" s="47" t="n"/>
-      <c r="F25" s="47" t="n"/>
-      <c r="G25" s="47" t="n"/>
-      <c r="H25" s="47" t="n"/>
-      <c r="I25" s="47" t="n"/>
-      <c r="J25" s="47" t="n"/>
-      <c r="K25" s="47" t="n"/>
-      <c r="L25" s="47" t="n"/>
+      <c r="A25" s="48" t="n"/>
+      <c r="B25" s="48" t="n"/>
+      <c r="C25" s="48" t="n"/>
+      <c r="D25" s="48" t="n"/>
+      <c r="E25" s="48" t="n"/>
+      <c r="F25" s="48" t="n"/>
+      <c r="G25" s="48" t="n"/>
+      <c r="H25" s="48" t="n"/>
+      <c r="I25" s="48" t="n"/>
+      <c r="J25" s="48" t="n"/>
+      <c r="K25" s="48" t="n"/>
+      <c r="L25" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3374,23 +3386,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'15-Year Property'!A1", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="59" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="60" t="inlineStr">
         <is>
           <t>Y1 SUMMARY</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'Form 4562 Mirror'!A1", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -3407,481 +3419,481 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr">
         <is>
           <t>Per-class Year 1 deduction with bonus overlay, vs. naive 27.5-year baseline. Settings drives the bonus % and marginal rate.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="54" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="B6" s="54" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
         <is>
           <t>Basis ($)</t>
         </is>
       </c>
-      <c r="C6" s="54" t="inlineStr">
+      <c r="C6" s="55" t="inlineStr">
         <is>
           <t>Bonus %</t>
         </is>
       </c>
-      <c r="D6" s="54" t="inlineStr">
+      <c r="D6" s="55" t="inlineStr">
         <is>
           <t>Bonus $</t>
         </is>
       </c>
-      <c r="E6" s="54" t="inlineStr">
+      <c r="E6" s="55" t="inlineStr">
         <is>
           <t>Non-bonus × MACRS Y1 %</t>
         </is>
       </c>
-      <c r="F6" s="54" t="inlineStr">
+      <c r="F6" s="55" t="inlineStr">
         <is>
           <t>Total Y1 ($)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="61" t="inlineStr">
+      <c r="A7" s="62" t="inlineStr">
         <is>
           <t>5-year</t>
         </is>
       </c>
-      <c r="B7" s="62">
+      <c r="B7" s="63">
         <f>'5-Year Property'!C20</f>
         <v/>
       </c>
-      <c r="C7" s="63">
+      <c r="C7" s="64">
         <f>Settings!$B$6</f>
         <v/>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="63">
         <f>B7*C7</f>
         <v/>
       </c>
-      <c r="E7" s="62">
+      <c r="E7" s="63">
         <f>(B7-D7)*Settings!$B$8</f>
         <v/>
       </c>
-      <c r="F7" s="64">
+      <c r="F7" s="65">
         <f>D7+E7</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="62" t="inlineStr">
         <is>
           <t>7-year</t>
         </is>
       </c>
-      <c r="B8" s="62">
+      <c r="B8" s="63">
         <f>'7-Year Property'!C18</f>
         <v/>
       </c>
-      <c r="C8" s="63">
+      <c r="C8" s="64">
         <f>Settings!$B$6</f>
         <v/>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="63">
         <f>B8*C8</f>
         <v/>
       </c>
-      <c r="E8" s="62">
+      <c r="E8" s="63">
         <f>(B8-D8)*Settings!$B$9</f>
         <v/>
       </c>
-      <c r="F8" s="64">
+      <c r="F8" s="65">
         <f>D8+E8</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="61" t="inlineStr">
+      <c r="A9" s="62" t="inlineStr">
         <is>
           <t>15-year</t>
         </is>
       </c>
-      <c r="B9" s="62">
+      <c r="B9" s="63">
         <f>'15-Year Property'!C18</f>
         <v/>
       </c>
-      <c r="C9" s="63">
+      <c r="C9" s="64">
         <f>Settings!$B$6</f>
         <v/>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="63">
         <f>B9*C9</f>
         <v/>
       </c>
-      <c r="E9" s="62">
+      <c r="E9" s="63">
         <f>(B9-D9)*Settings!$B$10</f>
         <v/>
       </c>
-      <c r="F9" s="64">
+      <c r="F9" s="65">
         <f>D9+E9</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="62" t="inlineStr">
         <is>
           <t>27.5-yr (residual)</t>
         </is>
       </c>
-      <c r="B10" s="62">
+      <c r="B10" s="63">
         <f>'Land Allocation'!B13-B7-B8-B9</f>
         <v/>
       </c>
-      <c r="C10" s="65" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="62" t="n">
+      <c r="D10" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="66">
+      <c r="E10" s="67">
         <f>IFERROR((12.5-MONTH('Property Basics'!B12))/12/27.5,0)</f>
         <v/>
       </c>
-      <c r="F10" s="64">
+      <c r="F10" s="65">
         <f>B10*E10</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>Land (non-depreciable)</t>
         </is>
       </c>
-      <c r="B11" s="68">
+      <c r="B11" s="69">
         <f>'Land Allocation'!B12</f>
         <v/>
       </c>
-      <c r="C11" s="65" t="inlineStr">
+      <c r="C11" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D11" s="65" t="inlineStr">
+      <c r="D11" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="65" t="inlineStr">
+      <c r="E11" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="65" t="inlineStr">
+      <c r="F11" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="69" t="inlineStr">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="70">
+      <c r="B12" s="71">
         <f>'Property Basics'!B10</f>
         <v/>
       </c>
-      <c r="C12" s="71" t="n"/>
-      <c r="D12" s="71" t="n"/>
-      <c r="E12" s="71" t="n"/>
-      <c r="F12" s="50">
+      <c r="C12" s="72" t="n"/>
+      <c r="D12" s="72" t="n"/>
+      <c r="E12" s="72" t="n"/>
+      <c r="F12" s="51">
         <f>SUM(F7:F10)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="53">
+      <c r="A14" s="54">
         <f>IFERROR(IF((B7+B8+B9)/'Land Allocation'!B13&gt;0.4,"⚠ Reclassification at "&amp;TEXT((B7+B8+B9)/'Land Allocation'!B13,"0.0%")&amp;" of improvements basis — above the typical 25–35% defensible range. Consider an engineer-led study (&gt;$750K acquisition) or reduce reclassifications.",""),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>NAIVE 27.5-YR BASELINE — WHAT YOU SAVED</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Naive Y1 deduction (everything at 27.5-yr):</t>
         </is>
       </c>
-      <c r="B17" s="32" t="n"/>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="32" t="n"/>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="72">
+      <c r="B17" s="33" t="n"/>
+      <c r="C17" s="33" t="n"/>
+      <c r="D17" s="33" t="n"/>
+      <c r="E17" s="33" t="n"/>
+      <c r="F17" s="73">
         <f>'Land Allocation'!B13*E10</f>
         <v/>
       </c>
-      <c r="G17" s="32" t="n"/>
-      <c r="H17" s="32" t="n"/>
-      <c r="I17" s="32" t="n"/>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="33" t="n"/>
+      <c r="G17" s="33" t="n"/>
+      <c r="H17" s="33" t="n"/>
+      <c r="I17" s="33" t="n"/>
+      <c r="J17" s="33" t="n"/>
+      <c r="K17" s="33" t="n"/>
+      <c r="L17" s="34" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>Accelerated Y1 deduction (this workbook):</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="48">
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="49">
         <f>F12</f>
         <v/>
       </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="36" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="37" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="38" t="inlineStr">
         <is>
           <t>EXTRA Y1 DEDUCTION:</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="50">
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="51">
         <f>F18-F17</f>
         <v/>
       </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="36" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="37" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="52" t="inlineStr">
         <is>
           <t>Y1 TAX SAVINGS @ marginal rate:</t>
         </is>
       </c>
-      <c r="B20" s="43" t="n"/>
-      <c r="C20" s="43" t="n"/>
-      <c r="D20" s="43" t="n"/>
-      <c r="E20" s="43" t="n"/>
-      <c r="F20" s="52">
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="44" t="n"/>
+      <c r="E20" s="44" t="n"/>
+      <c r="F20" s="53">
         <f>F19*Settings!$B$7</f>
         <v/>
       </c>
-      <c r="G20" s="43" t="n"/>
-      <c r="H20" s="43" t="n"/>
-      <c r="I20" s="43" t="n"/>
-      <c r="J20" s="43" t="n"/>
-      <c r="K20" s="43" t="n"/>
-      <c r="L20" s="44" t="n"/>
+      <c r="G20" s="44" t="n"/>
+      <c r="H20" s="44" t="n"/>
+      <c r="I20" s="44" t="n"/>
+      <c r="J20" s="44" t="n"/>
+      <c r="K20" s="44" t="n"/>
+      <c r="L20" s="45" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>5-YEAR MACRS SCHEDULE (NON-BONUS PORTIONS)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="54" t="inlineStr">
+      <c r="A24" s="55" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B24" s="54" t="inlineStr">
+      <c r="B24" s="55" t="inlineStr">
         <is>
           <t>5-yr</t>
         </is>
       </c>
-      <c r="C24" s="54" t="inlineStr">
+      <c r="C24" s="55" t="inlineStr">
         <is>
           <t>7-yr</t>
         </is>
       </c>
-      <c r="D24" s="54" t="inlineStr">
+      <c r="D24" s="55" t="inlineStr">
         <is>
           <t>15-yr</t>
         </is>
       </c>
-      <c r="E24" s="54" t="inlineStr">
+      <c r="E24" s="55" t="inlineStr">
         <is>
           <t>27.5-yr (bldg)</t>
         </is>
       </c>
-      <c r="F24" s="54" t="inlineStr">
+      <c r="F24" s="55" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="55" t="inlineStr">
+      <c r="A25" s="56" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="B25" s="48">
+      <c r="B25" s="49">
         <f>(B7-D7)*0.2</f>
         <v/>
       </c>
-      <c r="C25" s="48">
+      <c r="C25" s="49">
         <f>(B8-D8)*0.1429</f>
         <v/>
       </c>
-      <c r="D25" s="48">
+      <c r="D25" s="49">
         <f>(B9-D9)*0.05</f>
         <v/>
       </c>
-      <c r="E25" s="48">
+      <c r="E25" s="49">
         <f>B10*E10</f>
         <v/>
       </c>
-      <c r="F25" s="73">
+      <c r="F25" s="74">
         <f>SUM(B25:E25)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="55" t="inlineStr">
+      <c r="A26" s="56" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="B26" s="48">
+      <c r="B26" s="49">
         <f>(B7-D7)*0.32</f>
         <v/>
       </c>
-      <c r="C26" s="48">
+      <c r="C26" s="49">
         <f>(B8-D8)*0.2449</f>
         <v/>
       </c>
-      <c r="D26" s="48">
+      <c r="D26" s="49">
         <f>(B9-D9)*0.095</f>
         <v/>
       </c>
-      <c r="E26" s="48">
+      <c r="E26" s="49">
         <f>B10/27.5</f>
         <v/>
       </c>
-      <c r="F26" s="73">
+      <c r="F26" s="74">
         <f>SUM(B26:E26)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="55" t="inlineStr">
+      <c r="A27" s="56" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="B27" s="48">
+      <c r="B27" s="49">
         <f>(B7-D7)*0.192</f>
         <v/>
       </c>
-      <c r="C27" s="48">
+      <c r="C27" s="49">
         <f>(B8-D8)*0.1749</f>
         <v/>
       </c>
-      <c r="D27" s="48">
+      <c r="D27" s="49">
         <f>(B9-D9)*0.0855</f>
         <v/>
       </c>
-      <c r="E27" s="48">
+      <c r="E27" s="49">
         <f>B10/27.5</f>
         <v/>
       </c>
-      <c r="F27" s="73">
+      <c r="F27" s="74">
         <f>SUM(B27:E27)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="55" t="inlineStr">
+      <c r="A28" s="56" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="B28" s="48">
+      <c r="B28" s="49">
         <f>(B7-D7)*0.1152</f>
         <v/>
       </c>
-      <c r="C28" s="48">
+      <c r="C28" s="49">
         <f>(B8-D8)*0.1249</f>
         <v/>
       </c>
-      <c r="D28" s="48">
+      <c r="D28" s="49">
         <f>(B9-D9)*0.077</f>
         <v/>
       </c>
-      <c r="E28" s="48">
+      <c r="E28" s="49">
         <f>B10/27.5</f>
         <v/>
       </c>
-      <c r="F28" s="73">
+      <c r="F28" s="74">
         <f>SUM(B28:E28)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="55" t="inlineStr">
+      <c r="A29" s="56" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
-      <c r="B29" s="48">
+      <c r="B29" s="49">
         <f>(B7-D7)*0.1152</f>
         <v/>
       </c>
-      <c r="C29" s="48">
+      <c r="C29" s="49">
         <f>(B8-D8)*0.0893</f>
         <v/>
       </c>
-      <c r="D29" s="48">
+      <c r="D29" s="49">
         <f>(B9-D9)*0.0693</f>
         <v/>
       </c>
-      <c r="E29" s="48">
+      <c r="E29" s="49">
         <f>B10/27.5</f>
         <v/>
       </c>
-      <c r="F29" s="73">
+      <c r="F29" s="74">
         <f>SUM(B29:E29)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="45" t="inlineStr">
+      <c r="A31" s="46" t="inlineStr">
         <is>
           <t>ⓘ Year 1 totals above show the NON-BONUS portions only — add the bonus depreciation row (F12 minus E10×B10 etc.) to get the full Y1 number from the table at the top. The Form 4562 Mirror tab consolidates everything into the IRS line items your CPA needs.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="45" t="inlineStr">
+      <c r="A33" s="46" t="inlineStr">
         <is>
           <t>ⓘ The 27.5-yr (bldg) Year 1 reflects the mid-month convention based on your placed-in-service month. Years 2+ use the full 1/27.5 = 3.636% annual rate. Bonus depreciation does NOT apply to the 27.5-yr residual (only to property with recovery period ≤ 20 years).</t>
         </is>
@@ -3947,23 +3959,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Y1 Summary'!A1", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="59" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="60" t="inlineStr">
         <is>
           <t>FORM 4562 MIRROR</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'Launch'!A1", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -3980,226 +3992,226 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr">
         <is>
           <t>IRS Form 4562 — Parts II (Bonus) and III (MACRS) for your CPA. Print this and attach to the asset detail.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C5" s="54" t="inlineStr">
+      <c r="C5" s="55" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="74" t="inlineStr">
+      <c r="A6" s="75" t="inlineStr">
         <is>
           <t xml:space="preserve">  Part II — PART II — SPECIAL DEPRECIATION (BONUS)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>14a</t>
         </is>
       </c>
-      <c r="B7" s="75" t="inlineStr">
+      <c r="B7" s="76" t="inlineStr">
         <is>
           <t>Bonus depr — 5-yr property:</t>
         </is>
       </c>
-      <c r="C7" s="62">
+      <c r="C7" s="63">
         <f>'Y1 Summary'!D7</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>14b</t>
         </is>
       </c>
-      <c r="B8" s="75" t="inlineStr">
+      <c r="B8" s="76" t="inlineStr">
         <is>
           <t>Bonus depr — 7-yr property:</t>
         </is>
       </c>
-      <c r="C8" s="62">
+      <c r="C8" s="63">
         <f>'Y1 Summary'!D8</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="55" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>14c</t>
         </is>
       </c>
-      <c r="B9" s="75" t="inlineStr">
+      <c r="B9" s="76" t="inlineStr">
         <is>
           <t>Bonus depr — 15-yr property:</t>
         </is>
       </c>
-      <c r="C9" s="62">
+      <c r="C9" s="63">
         <f>'Y1 Summary'!D9</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B10" s="76" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>Total bonus depreciation (sum 14a–14c):</t>
         </is>
       </c>
-      <c r="C10" s="77">
+      <c r="C10" s="78">
         <f>'Y1 Summary'!D7+'Y1 Summary'!D8+'Y1 Summary'!D9</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="74" t="inlineStr">
+      <c r="A11" s="75" t="inlineStr">
         <is>
           <t xml:space="preserve">  Part III — PART III — MACRS DEPRECIATION (CURRENT YEAR)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>19a</t>
         </is>
       </c>
-      <c r="B12" s="75" t="inlineStr">
+      <c r="B12" s="76" t="inlineStr">
         <is>
           <t>5-year property — non-bonus basis × Y1 %:</t>
         </is>
       </c>
-      <c r="C12" s="62">
+      <c r="C12" s="63">
         <f>'Y1 Summary'!E7</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="55" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>19b</t>
         </is>
       </c>
-      <c r="B13" s="75" t="inlineStr">
+      <c r="B13" s="76" t="inlineStr">
         <is>
           <t>7-year property — non-bonus basis × Y1 %:</t>
         </is>
       </c>
-      <c r="C13" s="62">
+      <c r="C13" s="63">
         <f>'Y1 Summary'!E8</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="55" t="inlineStr">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t>19c</t>
         </is>
       </c>
-      <c r="B14" s="75" t="inlineStr">
+      <c r="B14" s="76" t="inlineStr">
         <is>
           <t>15-year property — non-bonus basis × Y1 %:</t>
         </is>
       </c>
-      <c r="C14" s="62">
+      <c r="C14" s="63">
         <f>'Y1 Summary'!E9</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="55" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>19h</t>
         </is>
       </c>
-      <c r="B15" s="76" t="inlineStr">
+      <c r="B15" s="77" t="inlineStr">
         <is>
           <t>27.5-yr residential (mid-month conv.):</t>
         </is>
       </c>
-      <c r="C15" s="77">
+      <c r="C15" s="78">
         <f>'Y1 Summary'!F10</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="55" t="inlineStr">
+      <c r="A16" s="56" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B16" s="76" t="inlineStr">
+      <c r="B16" s="77" t="inlineStr">
         <is>
           <t>Total MACRS this year (sum 19a–19h):</t>
         </is>
       </c>
-      <c r="C16" s="77">
+      <c r="C16" s="78">
         <f>'Y1 Summary'!E7+'Y1 Summary'!E8+'Y1 Summary'!E9+'Y1 Summary'!F10</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="74" t="inlineStr">
+      <c r="A17" s="75" t="inlineStr">
         <is>
           <t xml:space="preserve">  Part IV — PART IV — SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="55" t="inlineStr">
+      <c r="A18" s="56" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B18" s="78" t="inlineStr">
+      <c r="B18" s="79" t="inlineStr">
         <is>
           <t>GRAND TOTAL Y1 DEDUCTION:</t>
         </is>
       </c>
-      <c r="C18" s="79">
+      <c r="C18" s="80">
         <f>'Y1 Summary'!F12</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="74" t="inlineStr">
+      <c r="A19" s="75" t="inlineStr">
         <is>
           <t xml:space="preserve">  Routing — ROUTING — where this lands on your return</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="80" t="inlineStr">
+      <c r="A20" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">  If Schedule E filer: Form 4562 → Sched E Line 18</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="80" t="inlineStr">
+      <c r="A21" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">  If Schedule C filer: Form 4562 → Sched C Line 13</t>
         </is>
@@ -4262,13 +4274,13 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Form 4562 Mirror'!A1", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="59" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="60" t="inlineStr">
         <is>
           <t>LAUNCH</t>
         </is>
@@ -4289,14 +4301,14 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="81" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>Your cost segregation is ready</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Print Form 4562 Mirror, complete the methodology block below, and hand both to your CPA.</t>
         </is>
@@ -4317,391 +4329,391 @@
       <c r="L6" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="82" t="inlineStr">
+      <c r="A9" s="83" t="inlineStr">
         <is>
           <t>TOTAL Y1 DEDUCTION</t>
         </is>
       </c>
-      <c r="B9" s="83" t="n"/>
-      <c r="C9" s="83" t="n"/>
-      <c r="D9" s="84" t="n"/>
-      <c r="E9" s="85" t="inlineStr">
+      <c r="B9" s="84" t="n"/>
+      <c r="C9" s="84" t="n"/>
+      <c r="D9" s="85" t="n"/>
+      <c r="E9" s="86" t="inlineStr">
         <is>
           <t>EXTRA vs. NAIVE 27.5-YR</t>
         </is>
       </c>
-      <c r="F9" s="83" t="n"/>
-      <c r="G9" s="83" t="n"/>
-      <c r="H9" s="84" t="n"/>
-      <c r="I9" s="85" t="inlineStr">
+      <c r="F9" s="84" t="n"/>
+      <c r="G9" s="84" t="n"/>
+      <c r="H9" s="85" t="n"/>
+      <c r="I9" s="86" t="inlineStr">
         <is>
           <t>Y1 TAX SAVINGS</t>
         </is>
       </c>
-      <c r="J9" s="83" t="n"/>
-      <c r="K9" s="83" t="n"/>
-      <c r="L9" s="84" t="n"/>
+      <c r="J9" s="84" t="n"/>
+      <c r="K9" s="84" t="n"/>
+      <c r="L9" s="85" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="86">
+      <c r="A10" s="87">
         <f>'Y1 Summary'!F12</f>
         <v/>
       </c>
-      <c r="B10" s="87" t="n"/>
-      <c r="C10" s="87" t="n"/>
-      <c r="D10" s="88" t="n"/>
-      <c r="E10" s="89">
+      <c r="B10" s="88" t="n"/>
+      <c r="C10" s="88" t="n"/>
+      <c r="D10" s="89" t="n"/>
+      <c r="E10" s="90">
         <f>'Y1 Summary'!F19</f>
         <v/>
       </c>
-      <c r="F10" s="87" t="n"/>
-      <c r="G10" s="87" t="n"/>
-      <c r="H10" s="88" t="n"/>
-      <c r="I10" s="89">
+      <c r="F10" s="88" t="n"/>
+      <c r="G10" s="88" t="n"/>
+      <c r="H10" s="89" t="n"/>
+      <c r="I10" s="90">
         <f>'Y1 Summary'!F20</f>
         <v/>
       </c>
-      <c r="J10" s="87" t="n"/>
-      <c r="K10" s="87" t="n"/>
-      <c r="L10" s="88" t="n"/>
+      <c r="J10" s="88" t="n"/>
+      <c r="K10" s="88" t="n"/>
+      <c r="L10" s="89" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="90" t="n"/>
-      <c r="B11" s="87" t="n"/>
-      <c r="C11" s="87" t="n"/>
-      <c r="D11" s="88" t="n"/>
-      <c r="E11" s="90" t="n"/>
-      <c r="F11" s="87" t="n"/>
-      <c r="G11" s="87" t="n"/>
-      <c r="H11" s="88" t="n"/>
-      <c r="I11" s="90" t="n"/>
-      <c r="J11" s="87" t="n"/>
-      <c r="K11" s="87" t="n"/>
-      <c r="L11" s="88" t="n"/>
+      <c r="A11" s="91" t="n"/>
+      <c r="B11" s="88" t="n"/>
+      <c r="C11" s="88" t="n"/>
+      <c r="D11" s="89" t="n"/>
+      <c r="E11" s="91" t="n"/>
+      <c r="F11" s="88" t="n"/>
+      <c r="G11" s="88" t="n"/>
+      <c r="H11" s="89" t="n"/>
+      <c r="I11" s="91" t="n"/>
+      <c r="J11" s="88" t="n"/>
+      <c r="K11" s="88" t="n"/>
+      <c r="L11" s="89" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="91" t="inlineStr">
+      <c r="A12" s="92" t="inlineStr">
         <is>
           <t>Bonus + MACRS, all classes</t>
         </is>
       </c>
-      <c r="B12" s="92" t="n"/>
-      <c r="C12" s="92" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="91" t="inlineStr">
+      <c r="B12" s="93" t="n"/>
+      <c r="C12" s="93" t="n"/>
+      <c r="D12" s="94" t="n"/>
+      <c r="E12" s="92" t="inlineStr">
         <is>
           <t>extra Y1 deduction this gives you</t>
         </is>
       </c>
-      <c r="F12" s="92" t="n"/>
-      <c r="G12" s="92" t="n"/>
-      <c r="H12" s="93" t="n"/>
-      <c r="I12" s="91" t="inlineStr">
+      <c r="F12" s="93" t="n"/>
+      <c r="G12" s="93" t="n"/>
+      <c r="H12" s="94" t="n"/>
+      <c r="I12" s="92" t="inlineStr">
         <is>
           <t>at your marginal rate (Settings)</t>
         </is>
       </c>
-      <c r="J12" s="92" t="n"/>
-      <c r="K12" s="92" t="n"/>
-      <c r="L12" s="93" t="n"/>
+      <c r="J12" s="93" t="n"/>
+      <c r="K12" s="93" t="n"/>
+      <c r="L12" s="94" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <f>HYPERLINK("#'Form 4562 Mirror'!A1", "📄  PRINT FORM 4562 MIRROR  →")</f>
         <v/>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="14" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
+      <c r="K16" s="15" t="n"/>
+      <c r="L16" s="15" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="14" t="n"/>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="14" t="n"/>
-      <c r="I17" s="14" t="n"/>
-      <c r="J17" s="14" t="n"/>
-      <c r="K17" s="14" t="n"/>
-      <c r="L17" s="14" t="n"/>
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
+      <c r="K17" s="15" t="n"/>
+      <c r="L17" s="15" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="14" t="n"/>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="14" t="n"/>
-      <c r="H18" s="14" t="n"/>
-      <c r="I18" s="14" t="n"/>
-      <c r="J18" s="14" t="n"/>
-      <c r="K18" s="14" t="n"/>
-      <c r="L18" s="14" t="n"/>
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="14" t="n"/>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-      <c r="H19" s="14" t="n"/>
-      <c r="I19" s="14" t="n"/>
-      <c r="J19" s="14" t="n"/>
-      <c r="K19" s="14" t="n"/>
-      <c r="L19" s="14" t="n"/>
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="n"/>
+      <c r="L19" s="15" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>AUDIT-DEFENSE — METHODOLOGY DISCLOSURE (SIGN + DATE)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="94" t="inlineStr">
+      <c r="A23" s="95" t="inlineStr">
         <is>
           <t>I used the DIY rule-of-thumb cost segregation method described in the IRS Cost Segregation Audit Techniques Guide. Allocations were derived from the sources checked below:</t>
         </is>
       </c>
-      <c r="B23" s="32" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="32" t="n"/>
-      <c r="I23" s="32" t="n"/>
-      <c r="J23" s="32" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="33" t="n"/>
+      <c r="B23" s="33" t="n"/>
+      <c r="C23" s="33" t="n"/>
+      <c r="D23" s="33" t="n"/>
+      <c r="E23" s="33" t="n"/>
+      <c r="F23" s="33" t="n"/>
+      <c r="G23" s="33" t="n"/>
+      <c r="H23" s="33" t="n"/>
+      <c r="I23" s="33" t="n"/>
+      <c r="J23" s="33" t="n"/>
+      <c r="K23" s="33" t="n"/>
+      <c r="L23" s="34" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="95" t="inlineStr">
+      <c r="A24" s="96" t="inlineStr">
         <is>
           <t>[ ] Purchase agreement / settlement statement (HUD-1 / Closing Disclosure)</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="36" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="7" t="n"/>
+      <c r="K24" s="7" t="n"/>
+      <c r="L24" s="37" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="95" t="inlineStr">
+      <c r="A25" s="96" t="inlineStr">
         <is>
           <t>[ ] Appraisal report (provides land + improvements split)</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="36" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="37" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="95" t="inlineStr">
+      <c r="A26" s="96" t="inlineStr">
         <is>
           <t>[ ] County tax assessor records (for land allocation ratio)</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="36" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="n"/>
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="37" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="95" t="inlineStr">
+      <c r="A27" s="96" t="inlineStr">
         <is>
           <t>[ ] Pre-purchase inspector report (itemized fixtures + components)</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="36" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="7" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="37" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="95" t="inlineStr">
+      <c r="A28" s="96" t="inlineStr">
         <is>
           <t>[ ] Vendor invoices for post-purchase furniture/appliances</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="36" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="37" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="95" t="inlineStr">
+      <c r="A29" s="96" t="inlineStr">
         <is>
           <t>[ ] Photographs with date metadata (before-rental documentation)</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="36" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="7" t="n"/>
+      <c r="K29" s="7" t="n"/>
+      <c r="L29" s="37" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="95" t="inlineStr">
+      <c r="A30" s="96" t="inlineStr">
         <is>
           <t>[ ] Industry benchmark percentages (RSMeans, AICPA, etc.)</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="36" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
+      <c r="K30" s="7" t="n"/>
+      <c r="L30" s="37" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="96" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="36" t="n"/>
+      <c r="A31" s="97" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
+      <c r="K31" s="7" t="n"/>
+      <c r="L31" s="37" t="n"/>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>Taxpayer signature:</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="97" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="36" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="98" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="7" t="n"/>
+      <c r="K32" s="7" t="n"/>
+      <c r="L32" s="37" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="41" t="inlineStr">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="B33" s="43" t="n"/>
-      <c r="C33" s="43" t="n"/>
-      <c r="D33" s="43" t="n"/>
-      <c r="E33" s="43" t="n"/>
-      <c r="F33" s="43" t="n"/>
-      <c r="G33" s="98" t="n"/>
-      <c r="H33" s="43" t="n"/>
-      <c r="I33" s="43" t="n"/>
-      <c r="J33" s="43" t="n"/>
-      <c r="K33" s="43" t="n"/>
-      <c r="L33" s="44" t="n"/>
+      <c r="B33" s="44" t="n"/>
+      <c r="C33" s="44" t="n"/>
+      <c r="D33" s="44" t="n"/>
+      <c r="E33" s="44" t="n"/>
+      <c r="F33" s="44" t="n"/>
+      <c r="G33" s="99" t="n"/>
+      <c r="H33" s="44" t="n"/>
+      <c r="I33" s="44" t="n"/>
+      <c r="J33" s="44" t="n"/>
+      <c r="K33" s="44" t="n"/>
+      <c r="L33" s="45" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>WHEN TO HIRE AN ENGINEER INSTEAD</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="99" t="inlineStr">
+      <c r="A36" s="100" t="inlineStr">
         <is>
           <t>Hire an engineer-led study (typical cost $3K–$8K) when ANY of the following:
   • Acquisition cost over $750K  •  Multi-building or multi-unit property
@@ -4710,131 +4722,131 @@
   • You've owned the property 5+ years and want a Form 3115 catch-up — engineer adds rigor</t>
         </is>
       </c>
-      <c r="B36" s="32" t="n"/>
-      <c r="C36" s="32" t="n"/>
-      <c r="D36" s="32" t="n"/>
-      <c r="E36" s="32" t="n"/>
-      <c r="F36" s="32" t="n"/>
-      <c r="G36" s="32" t="n"/>
-      <c r="H36" s="32" t="n"/>
-      <c r="I36" s="32" t="n"/>
-      <c r="J36" s="32" t="n"/>
-      <c r="K36" s="32" t="n"/>
-      <c r="L36" s="33" t="n"/>
+      <c r="B36" s="33" t="n"/>
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="33" t="n"/>
+      <c r="H36" s="33" t="n"/>
+      <c r="I36" s="33" t="n"/>
+      <c r="J36" s="33" t="n"/>
+      <c r="K36" s="33" t="n"/>
+      <c r="L36" s="34" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="96" t="n"/>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="36" t="n"/>
+      <c r="A37" s="97" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="7" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="37" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="100" t="n"/>
-      <c r="B38" s="43" t="n"/>
-      <c r="C38" s="43" t="n"/>
-      <c r="D38" s="43" t="n"/>
-      <c r="E38" s="43" t="n"/>
-      <c r="F38" s="43" t="n"/>
-      <c r="G38" s="43" t="n"/>
-      <c r="H38" s="43" t="n"/>
-      <c r="I38" s="43" t="n"/>
-      <c r="J38" s="43" t="n"/>
-      <c r="K38" s="43" t="n"/>
-      <c r="L38" s="44" t="n"/>
+      <c r="A38" s="101" t="n"/>
+      <c r="B38" s="44" t="n"/>
+      <c r="C38" s="44" t="n"/>
+      <c r="D38" s="44" t="n"/>
+      <c r="E38" s="44" t="n"/>
+      <c r="F38" s="44" t="n"/>
+      <c r="G38" s="44" t="n"/>
+      <c r="H38" s="44" t="n"/>
+      <c r="I38" s="44" t="n"/>
+      <c r="J38" s="44" t="n"/>
+      <c r="K38" s="44" t="n"/>
+      <c r="L38" s="45" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>OWNED 1+ YEARS? FORM 3115 RETROACTIVE CATCH-UP</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="99" t="inlineStr">
+      <c r="A41" s="100" t="inlineStr">
         <is>
           <t>If you've already filed returns depreciating this property at the default 27.5-yr, you can apply this cost-seg retroactively via Form 3115 (Application for Change in Accounting Method) with an IRC §481(a) catch-up adjustment.
   • The catch-up is the difference between accumulated depreciation under the new method vs. what you've already deducted — claimed in a single year on the year of change.
   • This workbook does NOT compute the §481(a) adjustment — the per-asset breakdown above is what your CPA needs to file Form 3115. Hand them both.</t>
         </is>
       </c>
-      <c r="B41" s="32" t="n"/>
-      <c r="C41" s="32" t="n"/>
-      <c r="D41" s="32" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="32" t="n"/>
-      <c r="H41" s="32" t="n"/>
-      <c r="I41" s="32" t="n"/>
-      <c r="J41" s="32" t="n"/>
-      <c r="K41" s="32" t="n"/>
-      <c r="L41" s="33" t="n"/>
+      <c r="B41" s="33" t="n"/>
+      <c r="C41" s="33" t="n"/>
+      <c r="D41" s="33" t="n"/>
+      <c r="E41" s="33" t="n"/>
+      <c r="F41" s="33" t="n"/>
+      <c r="G41" s="33" t="n"/>
+      <c r="H41" s="33" t="n"/>
+      <c r="I41" s="33" t="n"/>
+      <c r="J41" s="33" t="n"/>
+      <c r="K41" s="33" t="n"/>
+      <c r="L41" s="34" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="96" t="n"/>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="n"/>
-      <c r="I42" s="6" t="n"/>
-      <c r="J42" s="6" t="n"/>
-      <c r="K42" s="6" t="n"/>
-      <c r="L42" s="36" t="n"/>
+      <c r="A42" s="97" t="n"/>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
+      <c r="J42" s="7" t="n"/>
+      <c r="K42" s="7" t="n"/>
+      <c r="L42" s="37" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="100" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="43" t="n"/>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
-      <c r="J43" s="43" t="n"/>
-      <c r="K43" s="43" t="n"/>
-      <c r="L43" s="44" t="n"/>
+      <c r="A43" s="101" t="n"/>
+      <c r="B43" s="44" t="n"/>
+      <c r="C43" s="44" t="n"/>
+      <c r="D43" s="44" t="n"/>
+      <c r="E43" s="44" t="n"/>
+      <c r="F43" s="44" t="n"/>
+      <c r="G43" s="44" t="n"/>
+      <c r="H43" s="44" t="n"/>
+      <c r="I43" s="44" t="n"/>
+      <c r="J43" s="44" t="n"/>
+      <c r="K43" s="44" t="n"/>
+      <c r="L43" s="45" t="n"/>
     </row>
     <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="101" t="inlineStr">
+      <c r="A46" s="102" t="inlineStr">
         <is>
           <t>💡 Upgrade to the Tax Season Bundle ($147) — TAX-001/002/003/009/010 + Schedule E workbook.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="n"/>
-      <c r="B48" s="20" t="n"/>
-      <c r="C48" s="20" t="n"/>
-      <c r="D48" s="20" t="n"/>
-      <c r="E48" s="20" t="n"/>
-      <c r="F48" s="20" t="n"/>
-      <c r="G48" s="20" t="n"/>
-      <c r="H48" s="20" t="n"/>
-      <c r="I48" s="20" t="n"/>
-      <c r="J48" s="20" t="n"/>
-      <c r="K48" s="20" t="n"/>
-      <c r="L48" s="20" t="n"/>
+      <c r="A48" s="21" t="n"/>
+      <c r="B48" s="21" t="n"/>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="21" t="n"/>
+      <c r="I48" s="21" t="n"/>
+      <c r="J48" s="21" t="n"/>
+      <c r="K48" s="21" t="n"/>
+      <c r="L48" s="21" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="22" t="inlineStr">
         <is>
           <t>Questions? hello@thestrledger.com</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="22" t="inlineStr">
+      <c r="A50" s="23" t="inlineStr">
         <is>
           <t>TAX-010 · v2.3 · Free updates forever</t>
         </is>
